--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,37 +1412,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>MEXICO 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Londrina x Ponte Preta</t>
+          <t>Puebla x Toluca</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1451,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K13" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="L13" t="n">
-        <v>20.83</v>
+        <v>19.23</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>0X1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1491,37 +1491,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>BRAZIL 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Puebla x Toluca</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Puebla</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Toluca</t>
-        </is>
-      </c>
+          <t>Londrina x Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,110 +1522,39 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="L14" t="n">
-        <v>19.23</v>
+        <v>9.52</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0X1</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BRAZIL 2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Londrina x Ponte Preta</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Match Odds (Away)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="M15" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>6x0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -543,37 +553,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rayo Vallecano x Espanyol</t>
+          <t>Wadi Degla x Arab Contractors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Arab Contractors</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,37 +592,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6.45</v>
+        <v>6.9</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>6.66</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6.66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,32 +647,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo x Abo Qair Semads</t>
+          <t>Rayo Vallecano x Espanyol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Abo Qair Semads</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -661,20 +681,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16.13</v>
+        <v>6.45</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,6 +712,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,22 +728,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GERMANY 3</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Duisburg x TSV Havelse</t>
+          <t>Al Ahly Cairo x Abo Qair Semads</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Abo Qair Semads</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -740,20 +762,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="L4" t="n">
-        <v>16.67</v>
+        <v>16.13</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -771,6 +793,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -785,22 +809,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SWEDEN 2</t>
+          <t>GERMANY 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Landskrona x Sundsvall</t>
+          <t>Duisburg x TSV Havelse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -819,20 +843,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L5" t="n">
-        <v>21.74</v>
+        <v>16.67</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +874,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,37 +885,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>POLAND 1</t>
+          <t>SWEDEN 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Korona Kielce x Gornik Zabrze</t>
+          <t>Landskrona x Sundsvall</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +924,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L6" t="n">
-        <v>6.45</v>
+        <v>21.74</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +955,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,37 +966,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ross Co x Queen of South</t>
+          <t>Al Masry x Al Ittihad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ross Co</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,37 +1005,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17.24</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8x0</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>6.66</v>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1055,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ipswich x Arsenal</t>
+          <t>Alaves x Valencia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1094,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>18.52</v>
+        <v>9.52</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1084,9 +1122,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>9.19</v>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1096,37 +1142,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>POLAND 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Reading x Brentford</t>
+          <t>Korona Kielce x Gornik Zabrze</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1181,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15.62</v>
+        <v>6.45</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1212,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,27 +1223,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Elche x Real Madrid</t>
+          <t>Ross Co x Queen of South</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Ross Co</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1214,20 +1262,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="L10" t="n">
-        <v>13.89</v>
+        <v>17.24</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>8x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1293,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1304,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Barranquilla x Independiente Yumbo</t>
+          <t>Ipswich x Arsenal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1343,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="L11" t="n">
-        <v>5.88</v>
+        <v>18.52</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1374,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,37 +1385,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>COPA LIBERTADORES</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CA Platense x Fluminense</t>
+          <t>Reading x Brentford</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1372,20 +1424,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="L12" t="n">
-        <v>5.26</v>
+        <v>15.62</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1403,6 +1455,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1466,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MEXICO 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Puebla x Toluca</t>
+          <t>Elche x Real Madrid</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Toluca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1505,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="L13" t="n">
-        <v>19.23</v>
+        <v>13.89</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0X1</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1482,6 +1536,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,29 +1547,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BRAZIL 2</t>
+          <t>COLOMBIA 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Londrina x Ponte Preta</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>Barranquilla x Independiente Yumbo</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Independiente Yumbo</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1522,43 +1586,280 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9.52</v>
+        <v>5.88</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COPA LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CA Platense x Fluminense</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Over 4.5 FT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="M15" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2x1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BRAZIL 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Londrina x Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Match Odds (Away)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="M16" t="n">
+        <v>100</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>6x0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>9.19</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>
       </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MEXICO 1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Puebla x Toluca</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Match Odds (Home)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>100</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0X1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -856,12 +856,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -937,12 +937,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8x0</t>
+          <t>8-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x4</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0X1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -775,12 +775,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -856,12 +856,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -937,12 +937,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8-0</t>
+          <t>8x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2x4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0X1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-15.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1107,19 +1107,19 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S8" t="n">
